--- a/data/trans_bre/P36B08_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P36B08_R-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,99</t>
+          <t>2,39</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 18,88</t>
+          <t>1,32; 17,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 15,56</t>
+          <t>-0,34; 14,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 12,08</t>
+          <t>-1,49; 11,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 6,8</t>
+          <t>-1,25; 5,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 33,27</t>
+          <t>2,02; 30,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 23,36</t>
+          <t>-0,04; 22,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 15,81</t>
+          <t>-1,74; 15,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 7,61</t>
+          <t>-1,32; 6,5</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,4</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,9; 18,5</t>
+          <t>5,34; 18,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 17,27</t>
+          <t>5,57; 17,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 15,47</t>
+          <t>4,03; 15,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 4,02</t>
+          <t>-2,5; 4,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,21; 43,95</t>
+          <t>11,96; 44,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,71; 33,43</t>
+          <t>9,51; 33,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,64; 23,75</t>
+          <t>5,5; 24,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 4,46</t>
+          <t>-2,61; 4,65</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,2</t>
+          <t>2,87</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 11,24</t>
+          <t>-2,58; 11,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 11,73</t>
+          <t>0,06; 11,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 11,72</t>
+          <t>-1,48; 11,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 7,44</t>
+          <t>-0,41; 6,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 16,63</t>
+          <t>-3,38; 16,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 15,43</t>
+          <t>0,15; 15,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 17,07</t>
+          <t>-1,9; 16,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 8,45</t>
+          <t>-0,44; 7,73</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>-0,48</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>-0,49%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 15,72</t>
+          <t>3,09; 15,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 12,74</t>
+          <t>0,76; 12,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 12,07</t>
+          <t>1,33; 12,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 2,43</t>
+          <t>-2,27; 1,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 24,43</t>
+          <t>4,33; 25,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 16,97</t>
+          <t>0,97; 17,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,13; 15,84</t>
+          <t>1,59; 15,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 2,51</t>
+          <t>-2,29; 1,67</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>-0,47</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-0,46%</t>
+          <t>-0,47%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 20,87</t>
+          <t>1,06; 21,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 18,47</t>
+          <t>-0,98; 17,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 5,5</t>
+          <t>-5,94; 5,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,49</t>
+          <t>-1,66; 0,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 44,81</t>
+          <t>1,63; 47,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 31,42</t>
+          <t>-1,42; 29,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 6,38</t>
+          <t>-6,41; 6,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,49</t>
+          <t>-1,66; 0,37</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,9; 19,47</t>
+          <t>3,81; 19,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,89; 18,52</t>
+          <t>3,71; 17,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 15,2</t>
+          <t>-2,56; 14,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,89</t>
+          <t>-1,39; 3,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,25; 32,64</t>
+          <t>5,48; 33,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,05; 27,17</t>
+          <t>5,27; 25,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 31,69</t>
+          <t>-4,12; 29,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 4,1</t>
+          <t>-1,41; 4,08</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,99</t>
+          <t>3,78</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 4,39</t>
+          <t>-5,16; 4,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,76; 13,11</t>
+          <t>3,5; 12,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,81; 13,45</t>
+          <t>2,61; 13,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 11,83</t>
+          <t>0,57; 7,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 5,95</t>
+          <t>-6,59; 5,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,01; 18,67</t>
+          <t>4,57; 17,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,25; 22,12</t>
+          <t>3,94; 22,63</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 14,0</t>
+          <t>0,64; 8,52</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>0,36</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-0,23%</t>
+          <t>0,37%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,02; 14,98</t>
+          <t>4,52; 14,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,12; 12,03</t>
+          <t>3,49; 12,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 4,34</t>
+          <t>-4,63; 4,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,38</t>
+          <t>-1,2; 1,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,71; 25,39</t>
+          <t>6,98; 23,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,28; 17,2</t>
+          <t>4,7; 17,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 5,84</t>
+          <t>-5,88; 5,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,42</t>
+          <t>-1,22; 1,97</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,61; 10,3</t>
+          <t>5,65; 10,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,26; 10,41</t>
+          <t>6,1; 10,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,07</t>
+          <t>2,83; 7,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 2,8</t>
+          <t>0,32; 2,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,8; 16,75</t>
+          <t>8,72; 16,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,66; 14,95</t>
+          <t>8,42; 14,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,0; 9,94</t>
+          <t>3,86; 10,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 3,0</t>
+          <t>0,33; 2,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P36B08_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P36B08_R-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas</t>
+          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas  [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales]</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
